--- a/data/trans_orig/PCS12_SP-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud física (SF12)</t>
+          <t>Puntuación media del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,93; 53,02</t>
+          <t>51,98; 53,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,28; 52,57</t>
+          <t>51,15; 52,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,53; 52,87</t>
+          <t>51,68; 52,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,64; 51,09</t>
+          <t>49,69; 51,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,77; 51,13</t>
+          <t>49,69; 51,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,52; 50,15</t>
+          <t>48,53; 50,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,58; 50,18</t>
+          <t>48,57; 50,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,29; 49,51</t>
+          <t>48,29; 49,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,02; 51,91</t>
+          <t>50,99; 51,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,02; 51,16</t>
+          <t>50,05; 51,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,26; 51,29</t>
+          <t>50,24; 51,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,15; 50,1</t>
+          <t>49,11; 50,13</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,34; 53,36</t>
+          <t>52,37; 53,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,44; 52,59</t>
+          <t>51,54; 52,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,12; 53,13</t>
+          <t>52,19; 53,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50,06; 52,41</t>
+          <t>50,02; 52,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,84; 50,99</t>
+          <t>49,74; 50,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,95; 50,18</t>
+          <t>48,84; 50,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,7; 51,03</t>
+          <t>49,68; 51,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,03; 50,08</t>
+          <t>48,95; 50,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,24; 52,06</t>
+          <t>51,26; 52,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,38; 51,31</t>
+          <t>50,38; 51,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,09; 51,94</t>
+          <t>51,08; 51,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,86; 51,02</t>
+          <t>49,9; 51,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,09; 53,22</t>
+          <t>52,08; 53,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,22; 53,51</t>
+          <t>52,17; 53,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,36; 53,5</t>
+          <t>52,41; 53,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,85; 52,36</t>
+          <t>50,93; 52,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,26; 50,66</t>
+          <t>49,22; 50,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,35; 50,86</t>
+          <t>49,42; 50,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,01; 51,52</t>
+          <t>50,05; 51,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,18; 52,16</t>
+          <t>50,21; 52,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,89; 51,82</t>
+          <t>50,89; 51,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51,02; 52,02</t>
+          <t>51,01; 51,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,37; 52,33</t>
+          <t>51,38; 52,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,81; 52,03</t>
+          <t>50,84; 52,1</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,54; 53,42</t>
+          <t>52,53; 53,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,59; 52,75</t>
+          <t>51,56; 52,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,27; 53,36</t>
+          <t>52,25; 53,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,69; 51,74</t>
+          <t>50,61; 51,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,8; 51,01</t>
+          <t>49,78; 51,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,18; 50,43</t>
+          <t>49,24; 50,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,02; 51,3</t>
+          <t>49,96; 51,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,74; 50,57</t>
+          <t>48,7; 50,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 52,06</t>
+          <t>51,27; 52,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,55; 51,38</t>
+          <t>50,56; 51,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,22; 52,09</t>
+          <t>51,2; 52,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,75; 50,82</t>
+          <t>49,79; 50,77</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,55; 53,04</t>
+          <t>52,53; 53,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,95; 52,53</t>
+          <t>51,96; 52,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,42; 52,96</t>
+          <t>52,38; 52,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,7; 51,6</t>
+          <t>50,61; 51,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,02; 50,67</t>
+          <t>50,03; 50,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,42; 50,09</t>
+          <t>49,38; 50,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,01; 50,74</t>
+          <t>50,04; 50,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,33; 50,37</t>
+          <t>49,35; 50,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,33; 51,77</t>
+          <t>51,35; 51,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,74; 51,23</t>
+          <t>50,74; 51,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,29; 51,78</t>
+          <t>51,29; 51,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,23; 50,84</t>
+          <t>50,23; 50,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,4</t>
+          <t>50,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,93</t>
+          <t>49,05</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,64</t>
+          <t>49,72</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,98; 53,04</t>
+          <t>51,98; 53,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,15; 52,56</t>
+          <t>51,26; 52,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,68; 52,9</t>
+          <t>51,64; 52,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,69; 51,16</t>
+          <t>49,69; 51,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,69; 51,06</t>
+          <t>49,73; 51,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,53; 50,22</t>
+          <t>48,44; 50,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,57; 50,22</t>
+          <t>48,56; 50,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,29; 49,5</t>
+          <t>48,39; 49,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,99; 51,87</t>
+          <t>51,06; 51,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,05; 51,13</t>
+          <t>50,08; 51,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,24; 51,3</t>
+          <t>50,28; 51,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,11; 50,13</t>
+          <t>49,15; 50,17</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,45</t>
+          <t>52,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,55</t>
+          <t>49,59</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,61</t>
+          <t>50,89</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,37; 53,38</t>
+          <t>52,4; 53,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,54; 52,66</t>
+          <t>51,49; 52,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,19; 53,12</t>
+          <t>52,04; 53,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50,02; 52,39</t>
+          <t>51,66; 52,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,74; 50,95</t>
+          <t>49,83; 51,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,84; 50,2</t>
+          <t>48,85; 50,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,68; 51,03</t>
+          <t>49,74; 51,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,95; 50,04</t>
+          <t>49,04; 50,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,26; 52,07</t>
+          <t>51,24; 52,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,38; 51,24</t>
+          <t>50,4; 51,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,08; 51,91</t>
+          <t>51,06; 51,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,9; 51,07</t>
+          <t>50,56; 51,24</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,67</t>
+          <t>51,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,14</t>
+          <t>50,36</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,37</t>
+          <t>51,06</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,08; 53,21</t>
+          <t>52,16; 53,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,17; 53,47</t>
+          <t>52,16; 53,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,41; 53,56</t>
+          <t>52,33; 53,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,93; 52,28</t>
+          <t>51,08; 52,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,22; 50,68</t>
+          <t>49,21; 50,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,42; 50,93</t>
+          <t>49,37; 50,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,05; 51,49</t>
+          <t>50,02; 51,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,21; 52,22</t>
+          <t>49,7; 50,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,89; 51,83</t>
+          <t>50,86; 51,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,38; 52,35</t>
+          <t>51,43; 52,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,84; 52,1</t>
+          <t>50,6; 51,53</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,21</t>
+          <t>51,35</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,4</t>
+          <t>49,03</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,23</t>
+          <t>50,12</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,53; 53,41</t>
+          <t>52,54; 53,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,56; 52,73</t>
+          <t>51,55; 52,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,25; 53,33</t>
+          <t>52,25; 53,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,61; 51,73</t>
+          <t>50,81; 51,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,78; 51,01</t>
+          <t>49,85; 51,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,24; 50,46</t>
+          <t>49,21; 50,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,96; 51,36</t>
+          <t>49,98; 51,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,7; 50,64</t>
+          <t>48,47; 49,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 52,05</t>
+          <t>51,25; 52,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,2; 52,11</t>
+          <t>51,23; 52,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,79; 50,77</t>
+          <t>49,75; 50,48</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51,24</t>
+          <t>51,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,8</t>
+          <t>49,49</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,5</t>
+          <t>50,48</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,53; 53,07</t>
+          <t>52,55; 53,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,96; 52,56</t>
+          <t>51,94; 52,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,38; 52,96</t>
+          <t>52,4; 52,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,61; 51,6</t>
+          <t>51,24; 51,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,03; 50,66</t>
+          <t>50,01; 50,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,38; 50,11</t>
+          <t>49,41; 50,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,04; 50,73</t>
+          <t>49,97; 50,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 50,43</t>
+          <t>49,18; 49,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,35; 51,77</t>
+          <t>51,34; 51,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,74; 51,19</t>
+          <t>50,73; 51,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,29; 51,75</t>
+          <t>51,29; 51,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,23; 50,85</t>
+          <t>50,28; 50,69</t>
         </is>
       </c>
     </row>
